--- a/public/profund-fund-model.xlsx
+++ b/public/profund-fund-model.xlsx
@@ -2950,7 +2950,7 @@
         <v>78</v>
       </c>
       <c r="B41" s="14">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C41" s="14">
         <v>1500000</v>
